--- a/src/attributions/attributions_ig_traj_242.xlsx
+++ b/src/attributions/attributions_ig_traj_242.xlsx
@@ -999,10 +999,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>-0.1852928629560283</v>
+        <v>-0.08920872236650992</v>
       </c>
       <c r="C2" t="n">
         <v>0</v>
@@ -1011,52 +1011,52 @@
         <v>-0</v>
       </c>
       <c r="E2" t="n">
-        <v>0.02582876708690129</v>
+        <v>-0.03535393031554283</v>
       </c>
       <c r="F2" t="n">
-        <v>0.394390953113316</v>
+        <v>0.1470065389119949</v>
       </c>
       <c r="G2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="H2" t="n">
         <v>0</v>
       </c>
       <c r="I2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K2" t="n">
-        <v>-0.1128965570658511</v>
+        <v>-0.0695151765217147</v>
       </c>
       <c r="L2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="M2" t="n">
         <v>-0</v>
       </c>
       <c r="N2" t="n">
-        <v>-0.01919334177669472</v>
+        <v>0.003133750619418936</v>
       </c>
       <c r="O2" t="n">
-        <v>0.3547551077851407</v>
+        <v>0.1725573767276029</v>
       </c>
       <c r="P2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Q2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="R2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="S2" t="n">
         <v>0</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.0004460942501916275</v>
+        <v>-0.06697945554658678</v>
       </c>
       <c r="U2" t="n">
         <v>-0</v>
@@ -1065,13 +1065,13 @@
         <v>-0</v>
       </c>
       <c r="W2" t="n">
-        <v>0.03634996973725504</v>
+        <v>0.01215085370069216</v>
       </c>
       <c r="X2" t="n">
-        <v>0.08546756277753539</v>
+        <v>0.06803336369282001</v>
       </c>
       <c r="Y2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z2" t="n">
         <v>0</v>
@@ -1080,22 +1080,22 @@
         <v>-0</v>
       </c>
       <c r="AB2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AC2" t="n">
-        <v>-0.05390177972879568</v>
+        <v>0.04546060268900982</v>
       </c>
       <c r="AD2" t="n">
         <v>-0</v>
       </c>
       <c r="AE2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AF2" t="n">
-        <v>-0.03307234229089386</v>
+        <v>0.08207504993885843</v>
       </c>
       <c r="AG2" t="n">
-        <v>-0.0288307940437839</v>
+        <v>0.09288754083117529</v>
       </c>
       <c r="AH2" t="n">
         <v>-0</v>
@@ -1107,25 +1107,25 @@
         <v>0</v>
       </c>
       <c r="AK2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AL2" t="n">
-        <v>-0.03707387212292311</v>
+        <v>-0.04837789329354446</v>
       </c>
       <c r="AM2" t="n">
         <v>0</v>
       </c>
       <c r="AN2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AO2" t="n">
-        <v>-0.05753342356777046</v>
+        <v>-0.07763688214489464</v>
       </c>
       <c r="AP2" t="n">
-        <v>0.1096357848139231</v>
+        <v>0.1239615423281385</v>
       </c>
       <c r="AQ2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AR2" t="n">
         <v>0</v>
@@ -1137,7 +1137,7 @@
         <v>0</v>
       </c>
       <c r="AU2" t="n">
-        <v>-0.2086874958361182</v>
+        <v>-0.2014117176320296</v>
       </c>
       <c r="AV2" t="n">
         <v>0</v>
@@ -1146,10 +1146,10 @@
         <v>-0</v>
       </c>
       <c r="AX2" t="n">
-        <v>0.05999034916951238</v>
+        <v>-0.04410099156144079</v>
       </c>
       <c r="AY2" t="n">
-        <v>0.3461053309459913</v>
+        <v>0.2552920801029094</v>
       </c>
       <c r="AZ2" t="n">
         <v>-0</v>
@@ -1164,22 +1164,22 @@
         <v>0</v>
       </c>
       <c r="BD2" t="n">
-        <v>-0.05014238649060095</v>
+        <v>0.08391158453746343</v>
       </c>
       <c r="BE2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BF2" t="n">
         <v>-0</v>
       </c>
       <c r="BG2" t="n">
-        <v>0.03701582662652745</v>
+        <v>0.08313384410495989</v>
       </c>
       <c r="BH2" t="n">
-        <v>0.06760242694194125</v>
+        <v>-0.01318528266031764</v>
       </c>
       <c r="BI2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BJ2" t="n">
         <v>-0</v>
@@ -1188,10 +1188,10 @@
         <v>0</v>
       </c>
       <c r="BL2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BM2" t="n">
-        <v>-0.1038385929670587</v>
+        <v>0.02339382865431045</v>
       </c>
       <c r="BN2" t="n">
         <v>0</v>
@@ -1200,40 +1200,40 @@
         <v>0</v>
       </c>
       <c r="BP2" t="n">
-        <v>-0.03508397396650156</v>
+        <v>-0.04739844655224227</v>
       </c>
       <c r="BQ2" t="n">
-        <v>-0.01104911625284774</v>
+        <v>0.02281736381799412</v>
       </c>
       <c r="BR2" t="n">
         <v>0</v>
       </c>
       <c r="BS2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BT2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BU2" t="n">
         <v>0</v>
       </c>
       <c r="BV2" t="n">
-        <v>-0.08795592375968471</v>
+        <v>-0.1282021947674001</v>
       </c>
       <c r="BW2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BX2" t="n">
         <v>-0</v>
       </c>
       <c r="BY2" t="n">
-        <v>0.05595578743204209</v>
+        <v>-0.01863689205189025</v>
       </c>
       <c r="BZ2" t="n">
-        <v>0.1953311053923986</v>
+        <v>0.1894897495592763</v>
       </c>
       <c r="CA2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CB2" t="n">
         <v>0</v>
@@ -1242,28 +1242,28 @@
         <v>-0</v>
       </c>
       <c r="CD2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CE2" t="n">
-        <v>0.06222120453216987</v>
+        <v>0.05280254830599772</v>
       </c>
       <c r="CF2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CG2" t="n">
         <v>0</v>
       </c>
       <c r="CH2" t="n">
-        <v>-0.0008345220360875479</v>
+        <v>0.008543842264296119</v>
       </c>
       <c r="CI2" t="n">
-        <v>-0.08376084544171912</v>
+        <v>-0.07016410240163842</v>
       </c>
       <c r="CJ2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CK2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CL2" t="n">
         <v>-0</v>
@@ -1272,7 +1272,7 @@
         <v>-0</v>
       </c>
       <c r="CN2" t="n">
-        <v>-0.003908750777014676</v>
+        <v>0.04485913961443281</v>
       </c>
       <c r="CO2" t="n">
         <v>0</v>
@@ -1281,16 +1281,16 @@
         <v>0</v>
       </c>
       <c r="CQ2" t="n">
-        <v>-0.02821183262280114</v>
+        <v>-0.03676040102302669</v>
       </c>
       <c r="CR2" t="n">
-        <v>0.03022034932286382</v>
+        <v>-0.0997934307097491</v>
       </c>
       <c r="CS2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CT2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CU2" t="n">
         <v>0</v>
@@ -1299,19 +1299,19 @@
         <v>0</v>
       </c>
       <c r="CW2" t="n">
-        <v>0.04485991350728786</v>
+        <v>0.05504623062603776</v>
       </c>
       <c r="CX2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CY2" t="n">
         <v>-0</v>
       </c>
       <c r="CZ2" t="n">
-        <v>-0.001798645482121685</v>
+        <v>-0.0022559747610559</v>
       </c>
       <c r="DA2" t="n">
-        <v>-0.09183100119236927</v>
+        <v>-0.06680436708434216</v>
       </c>
       <c r="DB2" t="n">
         <v>0</v>
@@ -1326,19 +1326,19 @@
         <v>-0</v>
       </c>
       <c r="DF2" t="n">
-        <v>0.05607597886721162</v>
+        <v>0.01952146233336197</v>
       </c>
       <c r="DG2" t="n">
         <v>0</v>
       </c>
       <c r="DH2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DI2" t="n">
-        <v>-0.0391966686817347</v>
+        <v>0.01723906904517694</v>
       </c>
       <c r="DJ2" t="n">
-        <v>-0.04094917843191646</v>
+        <v>0.01266946360199546</v>
       </c>
       <c r="DK2" t="n">
         <v>-0</v>
@@ -1347,160 +1347,160 @@
         <v>-0</v>
       </c>
       <c r="DM2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DN2" t="n">
         <v>-0</v>
       </c>
       <c r="DO2" t="n">
-        <v>0.02703800142377881</v>
+        <v>-0.01029760466352246</v>
       </c>
       <c r="DP2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DQ2" t="n">
         <v>-0</v>
       </c>
       <c r="DR2" t="n">
-        <v>0.07429114256175705</v>
+        <v>-0.01286740051230992</v>
       </c>
       <c r="DS2" t="n">
-        <v>-0.0260253361160034</v>
+        <v>-0.05578461879962335</v>
       </c>
       <c r="DT2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DU2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DV2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DW2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DX2" t="n">
-        <v>0.05664729029473118</v>
+        <v>0.0003974437486490966</v>
       </c>
       <c r="DY2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DZ2" t="n">
         <v>-0</v>
       </c>
       <c r="EA2" t="n">
-        <v>-0.007615338719262414</v>
+        <v>0.01156549099442299</v>
       </c>
       <c r="EB2" t="n">
-        <v>-0.05664677759403061</v>
+        <v>-0.03182671913112185</v>
       </c>
       <c r="EC2" t="n">
         <v>-0</v>
       </c>
       <c r="ED2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EE2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EF2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EG2" t="n">
-        <v>0.03243588776027561</v>
+        <v>0.01940800706312987</v>
       </c>
       <c r="EH2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EI2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EJ2" t="n">
-        <v>-0.04519555805813455</v>
+        <v>-0.005765391518871962</v>
       </c>
       <c r="EK2" t="n">
-        <v>-0.04982625576651859</v>
+        <v>0.02171957682084159</v>
       </c>
       <c r="EL2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EM2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EN2" t="n">
         <v>0</v>
       </c>
       <c r="EO2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EP2" t="n">
-        <v>0.03250460189936297</v>
+        <v>0.0388507239001733</v>
       </c>
       <c r="EQ2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="ER2" t="n">
         <v>0</v>
       </c>
       <c r="ES2" t="n">
-        <v>0.05892711799827492</v>
+        <v>0.02916853279048108</v>
       </c>
       <c r="ET2" t="n">
-        <v>-0.03894823201917998</v>
+        <v>-0.006134483327101744</v>
       </c>
       <c r="EU2" t="n">
         <v>-0</v>
       </c>
       <c r="EV2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EW2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EX2" t="n">
         <v>-0</v>
       </c>
       <c r="EY2" t="n">
-        <v>0.04242340100665164</v>
+        <v>0.06028544046562436</v>
       </c>
       <c r="EZ2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FA2" t="n">
         <v>0</v>
       </c>
       <c r="FB2" t="n">
-        <v>-0.006116152209412397</v>
+        <v>0.02311039719332679</v>
       </c>
       <c r="FC2" t="n">
-        <v>-0.08712333707764303</v>
+        <v>-0.07262464045639729</v>
       </c>
       <c r="FD2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FE2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FF2" t="n">
         <v>0</v>
       </c>
       <c r="FG2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FH2" t="n">
-        <v>0.04100419002267879</v>
+        <v>0.07606518708535687</v>
       </c>
       <c r="FI2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FJ2" t="n">
         <v>0</v>
       </c>
       <c r="FK2" t="n">
-        <v>0.009340348950392142</v>
+        <v>-0.0004547327749609451</v>
       </c>
       <c r="FL2" t="n">
-        <v>0.04732777467721131</v>
+        <v>0.08127914370683728</v>
       </c>
       <c r="FM2" t="n">
         <v>0</v>
@@ -1515,7 +1515,7 @@
         <v>-0</v>
       </c>
       <c r="FQ2" t="n">
-        <v>0.04330085190599491</v>
+        <v>0.1201518661517752</v>
       </c>
       <c r="FR2" t="n">
         <v>0</v>
@@ -1524,43 +1524,43 @@
         <v>0</v>
       </c>
       <c r="FT2" t="n">
-        <v>0.005509220688679465</v>
+        <v>0.0249653781814968</v>
       </c>
       <c r="FU2" t="n">
-        <v>0.00307600396357208</v>
+        <v>0.001430919036967586</v>
       </c>
       <c r="FV2" t="n">
         <v>0</v>
       </c>
       <c r="FW2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FX2" t="n">
         <v>-0</v>
       </c>
       <c r="FY2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FZ2" t="n">
-        <v>0.005768010826467773</v>
+        <v>0.0564685545748517</v>
       </c>
       <c r="GA2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GB2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GC2" t="n">
         <v>-0</v>
       </c>
       <c r="GD2" t="n">
-        <v>0.05229668438109258</v>
+        <v>-0.01693609262868594</v>
       </c>
       <c r="GE2" t="n">
         <v>0</v>
       </c>
       <c r="GF2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GG2" t="n">
         <v>-0</v>
@@ -1568,10 +1568,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="B3" t="n">
-        <v>0.2878147212338333</v>
+        <v>0.3592665774559661</v>
       </c>
       <c r="C3" t="n">
         <v>0</v>
@@ -1580,10 +1580,10 @@
         <v>0</v>
       </c>
       <c r="E3" t="n">
-        <v>-0.06903426678540173</v>
+        <v>0.0124110029667905</v>
       </c>
       <c r="F3" t="n">
-        <v>-0.1861605570832192</v>
+        <v>-0.3185349832123135</v>
       </c>
       <c r="G3" t="n">
         <v>-0</v>
@@ -1592,13 +1592,13 @@
         <v>-0</v>
       </c>
       <c r="I3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="K3" t="n">
-        <v>0.2577700144135838</v>
+        <v>0.4887661062873814</v>
       </c>
       <c r="L3" t="n">
         <v>0</v>
@@ -1607,25 +1607,25 @@
         <v>0</v>
       </c>
       <c r="N3" t="n">
-        <v>-0.01676982683713597</v>
+        <v>-0.06469976493982263</v>
       </c>
       <c r="O3" t="n">
-        <v>-0.1812069610603313</v>
+        <v>-0.408413885587264</v>
       </c>
       <c r="P3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Q3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="R3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="S3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="T3" t="n">
-        <v>0.02997240260031061</v>
+        <v>0.1348631657901264</v>
       </c>
       <c r="U3" t="n">
         <v>0</v>
@@ -1634,67 +1634,67 @@
         <v>0</v>
       </c>
       <c r="W3" t="n">
-        <v>-0.01091782248889533</v>
+        <v>-0.08997640117938424</v>
       </c>
       <c r="X3" t="n">
-        <v>-0.01066161805841402</v>
+        <v>-0.0684747771039094</v>
       </c>
       <c r="Y3" t="n">
         <v>-0</v>
       </c>
       <c r="Z3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AB3" t="n">
         <v>-0</v>
       </c>
       <c r="AC3" t="n">
-        <v>0.01514748725954933</v>
+        <v>-0.02099978615454538</v>
       </c>
       <c r="AD3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AE3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AF3" t="n">
-        <v>0.03799535978859657</v>
+        <v>-0.2762934213857937</v>
       </c>
       <c r="AG3" t="n">
-        <v>0.004067049017134807</v>
+        <v>0.09734500500817471</v>
       </c>
       <c r="AH3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AI3" t="n">
         <v>-0</v>
       </c>
       <c r="AJ3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AK3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AL3" t="n">
-        <v>0.04255185539692295</v>
+        <v>0.1238131272451377</v>
       </c>
       <c r="AM3" t="n">
         <v>-0</v>
       </c>
       <c r="AN3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AO3" t="n">
-        <v>-0.004216380830539836</v>
+        <v>-0.05949332035183696</v>
       </c>
       <c r="AP3" t="n">
-        <v>-0.0639193299035308</v>
+        <v>-0.08840890567862766</v>
       </c>
       <c r="AQ3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AR3" t="n">
         <v>-0</v>
@@ -1703,37 +1703,37 @@
         <v>0</v>
       </c>
       <c r="AT3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AU3" t="n">
-        <v>0.2284602772073094</v>
+        <v>0.6463937434838852</v>
       </c>
       <c r="AV3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AW3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AX3" t="n">
-        <v>-0.01842010448539014</v>
+        <v>-0.2885792206392588</v>
       </c>
       <c r="AY3" t="n">
-        <v>-0.07901639720775332</v>
+        <v>-0.1997911008837412</v>
       </c>
       <c r="AZ3" t="n">
         <v>0</v>
       </c>
       <c r="BA3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BB3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BC3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BD3" t="n">
-        <v>0.05833942486599913</v>
+        <v>-0.1126946781311991</v>
       </c>
       <c r="BE3" t="n">
         <v>0</v>
@@ -1742,64 +1742,64 @@
         <v>0</v>
       </c>
       <c r="BG3" t="n">
-        <v>-0.06472983427533363</v>
+        <v>-0.02566080516115521</v>
       </c>
       <c r="BH3" t="n">
-        <v>-0.08219059373657751</v>
+        <v>-0.03750661578764619</v>
       </c>
       <c r="BI3" t="n">
         <v>0</v>
       </c>
       <c r="BJ3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BK3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BL3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BM3" t="n">
-        <v>0.04620553626372256</v>
+        <v>0.1267599079000587</v>
       </c>
       <c r="BN3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BO3" t="n">
         <v>-0</v>
       </c>
       <c r="BP3" t="n">
-        <v>0.01785785903410116</v>
+        <v>0.07541834802918621</v>
       </c>
       <c r="BQ3" t="n">
-        <v>0.005465321145655151</v>
+        <v>0.04127890339293192</v>
       </c>
       <c r="BR3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BS3" t="n">
         <v>-0</v>
       </c>
       <c r="BT3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BU3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BV3" t="n">
-        <v>0.114615607703585</v>
+        <v>0.3700263990427802</v>
       </c>
       <c r="BW3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BX3" t="n">
         <v>0</v>
       </c>
       <c r="BY3" t="n">
-        <v>-0.02948840970321008</v>
+        <v>-0.03550810160760057</v>
       </c>
       <c r="BZ3" t="n">
-        <v>-0.04878079628020656</v>
+        <v>-0.182342771419829</v>
       </c>
       <c r="CA3" t="n">
         <v>-0</v>
@@ -1808,28 +1808,28 @@
         <v>-0</v>
       </c>
       <c r="CC3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CD3" t="n">
         <v>0</v>
       </c>
       <c r="CE3" t="n">
-        <v>-0.0648703088395393</v>
+        <v>-0.1485052524197779</v>
       </c>
       <c r="CF3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CG3" t="n">
         <v>-0</v>
       </c>
       <c r="CH3" t="n">
-        <v>-0.007721770691504358</v>
+        <v>0.03170414698786368</v>
       </c>
       <c r="CI3" t="n">
-        <v>0.03872908045458783</v>
+        <v>0.10798569496285</v>
       </c>
       <c r="CJ3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CK3" t="n">
         <v>0</v>
@@ -1841,73 +1841,73 @@
         <v>0</v>
       </c>
       <c r="CN3" t="n">
-        <v>0.003525744495956261</v>
+        <v>-0.1446464043346002</v>
       </c>
       <c r="CO3" t="n">
         <v>-0</v>
       </c>
       <c r="CP3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CQ3" t="n">
-        <v>-0.01611087152957932</v>
+        <v>0.1146393546140499</v>
       </c>
       <c r="CR3" t="n">
-        <v>-0.05644652086419788</v>
+        <v>0.02857141539470635</v>
       </c>
       <c r="CS3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CT3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CU3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CV3" t="n">
         <v>-0</v>
       </c>
       <c r="CW3" t="n">
-        <v>-0.05921382478101779</v>
+        <v>-0.1404595684646018</v>
       </c>
       <c r="CX3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CY3" t="n">
         <v>0</v>
       </c>
       <c r="CZ3" t="n">
-        <v>-0.007590635846527114</v>
+        <v>0.01524570695447108</v>
       </c>
       <c r="DA3" t="n">
-        <v>0.0401456629436726</v>
+        <v>0.1398991042049428</v>
       </c>
       <c r="DB3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DC3" t="n">
         <v>-0</v>
       </c>
       <c r="DD3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DE3" t="n">
         <v>0</v>
       </c>
       <c r="DF3" t="n">
-        <v>-0.03323712693232195</v>
+        <v>-0.1112803389875733</v>
       </c>
       <c r="DG3" t="n">
         <v>0</v>
       </c>
       <c r="DH3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DI3" t="n">
-        <v>0.06211845463833868</v>
+        <v>-0.05844885863992825</v>
       </c>
       <c r="DJ3" t="n">
-        <v>0.04859796409482577</v>
+        <v>0.08664942347776897</v>
       </c>
       <c r="DK3" t="n">
         <v>0</v>
@@ -1916,13 +1916,13 @@
         <v>0</v>
       </c>
       <c r="DM3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DN3" t="n">
         <v>-0</v>
       </c>
       <c r="DO3" t="n">
-        <v>-0.02722390994583234</v>
+        <v>-0.08910546458876216</v>
       </c>
       <c r="DP3" t="n">
         <v>0</v>
@@ -1931,94 +1931,94 @@
         <v>0</v>
       </c>
       <c r="DR3" t="n">
-        <v>0.02287095351202065</v>
+        <v>-0.0005639195766592671</v>
       </c>
       <c r="DS3" t="n">
-        <v>0.01431597885538048</v>
+        <v>0.1093306977228302</v>
       </c>
       <c r="DT3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DU3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DV3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DW3" t="n">
         <v>-0</v>
       </c>
       <c r="DX3" t="n">
-        <v>-0.05460411774411725</v>
+        <v>-0.06335993665451449</v>
       </c>
       <c r="DY3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DZ3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EA3" t="n">
-        <v>0.01521494923011018</v>
+        <v>-0.007427109329146578</v>
       </c>
       <c r="EB3" t="n">
-        <v>0.03231451210163941</v>
+        <v>0.0352411578116134</v>
       </c>
       <c r="EC3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="ED3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EE3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EF3" t="n">
         <v>0</v>
       </c>
       <c r="EG3" t="n">
-        <v>-0.06896587327047683</v>
+        <v>-0.03320885329837635</v>
       </c>
       <c r="EH3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EI3" t="n">
         <v>-0</v>
       </c>
       <c r="EJ3" t="n">
-        <v>0.02754018855389256</v>
+        <v>-0.02386518241475493</v>
       </c>
       <c r="EK3" t="n">
-        <v>0.0253394665324788</v>
+        <v>0.02759106305415946</v>
       </c>
       <c r="EL3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EM3" t="n">
         <v>-0</v>
       </c>
       <c r="EN3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EO3" t="n">
         <v>0</v>
       </c>
       <c r="EP3" t="n">
-        <v>-0.05035544475187786</v>
+        <v>-0.05758744597421768</v>
       </c>
       <c r="EQ3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ER3" t="n">
         <v>-0</v>
       </c>
       <c r="ES3" t="n">
-        <v>-0.03500058140180162</v>
+        <v>-0.07571519355732911</v>
       </c>
       <c r="ET3" t="n">
-        <v>0.008463769422931347</v>
+        <v>-0.008201805572983724</v>
       </c>
       <c r="EU3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EV3" t="n">
         <v>0</v>
@@ -2030,46 +2030,46 @@
         <v>0</v>
       </c>
       <c r="EY3" t="n">
-        <v>-0.05914737327037439</v>
+        <v>-0.1689420317745762</v>
       </c>
       <c r="EZ3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FA3" t="n">
         <v>-0</v>
       </c>
       <c r="FB3" t="n">
-        <v>-0.001121468935411549</v>
+        <v>-0.006821154732513475</v>
       </c>
       <c r="FC3" t="n">
-        <v>0.03988739638894542</v>
+        <v>0.1216136351736869</v>
       </c>
       <c r="FD3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FE3" t="n">
         <v>0</v>
       </c>
       <c r="FF3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FG3" t="n">
         <v>0</v>
       </c>
       <c r="FH3" t="n">
-        <v>-0.03157828800321573</v>
+        <v>0.113972084665418</v>
       </c>
       <c r="FI3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FJ3" t="n">
         <v>-0</v>
       </c>
       <c r="FK3" t="n">
-        <v>0.007263258386767567</v>
+        <v>-0.06401186692973805</v>
       </c>
       <c r="FL3" t="n">
-        <v>0.03666540696353879</v>
+        <v>0.1740780511956319</v>
       </c>
       <c r="FM3" t="n">
         <v>0</v>
@@ -2081,10 +2081,10 @@
         <v>0</v>
       </c>
       <c r="FP3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FQ3" t="n">
-        <v>-0.000422044898886936</v>
+        <v>0.009837011797909613</v>
       </c>
       <c r="FR3" t="n">
         <v>-0</v>
@@ -2093,37 +2093,37 @@
         <v>-0</v>
       </c>
       <c r="FT3" t="n">
-        <v>-0.002354695548638968</v>
+        <v>-0.007780681991905951</v>
       </c>
       <c r="FU3" t="n">
-        <v>0.04851509601175726</v>
+        <v>-0.0723317750183132</v>
       </c>
       <c r="FV3" t="n">
         <v>-0</v>
       </c>
       <c r="FW3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FX3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FY3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FZ3" t="n">
-        <v>0.0005669519955003551</v>
+        <v>-0.02381991724614782</v>
       </c>
       <c r="GA3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GB3" t="n">
         <v>-0</v>
       </c>
       <c r="GC3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GD3" t="n">
-        <v>-0.04211418995605395</v>
+        <v>0.1680208705088072</v>
       </c>
       <c r="GE3" t="n">
         <v>-0</v>
@@ -2132,7 +2132,7 @@
         <v>-0</v>
       </c>
       <c r="GG3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4">
@@ -2140,7 +2140,7 @@
         <v>0</v>
       </c>
       <c r="B4" t="n">
-        <v>0.4870340664615532</v>
+        <v>0.3451182324101872</v>
       </c>
       <c r="C4" t="n">
         <v>0</v>
@@ -2149,16 +2149,16 @@
         <v>0</v>
       </c>
       <c r="E4" t="n">
-        <v>-0.1171038079518017</v>
+        <v>-0.02415007276200525</v>
       </c>
       <c r="F4" t="n">
-        <v>-0.4436249964418046</v>
+        <v>-0.1423975481477552</v>
       </c>
       <c r="G4" t="n">
         <v>-0</v>
       </c>
       <c r="H4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="I4" t="n">
         <v>0</v>
@@ -2167,7 +2167,7 @@
         <v>0</v>
       </c>
       <c r="K4" t="n">
-        <v>0.4564442769178869</v>
+        <v>0.4556398729406052</v>
       </c>
       <c r="L4" t="n">
         <v>0</v>
@@ -2176,25 +2176,25 @@
         <v>0</v>
       </c>
       <c r="N4" t="n">
-        <v>-0.05570592675916219</v>
+        <v>-0.1057542333602102</v>
       </c>
       <c r="O4" t="n">
-        <v>-0.4518573142021146</v>
+        <v>-0.2037387679502438</v>
       </c>
       <c r="P4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Q4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="R4" t="n">
         <v>0</v>
       </c>
       <c r="S4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="T4" t="n">
-        <v>0.03678668043720053</v>
+        <v>0.0994621737550056</v>
       </c>
       <c r="U4" t="n">
         <v>0</v>
@@ -2203,16 +2203,16 @@
         <v>0</v>
       </c>
       <c r="W4" t="n">
-        <v>-0.08439262822239568</v>
+        <v>-0.1181451646230026</v>
       </c>
       <c r="X4" t="n">
-        <v>-0.01567068857811676</v>
+        <v>-0.01165391202914747</v>
       </c>
       <c r="Y4" t="n">
         <v>-0</v>
       </c>
       <c r="Z4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA4" t="n">
         <v>0</v>
@@ -2221,19 +2221,19 @@
         <v>0</v>
       </c>
       <c r="AC4" t="n">
-        <v>-0.02363507836424826</v>
+        <v>-0.03181093238320283</v>
       </c>
       <c r="AD4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AE4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AF4" t="n">
-        <v>-0.01012467495818293</v>
+        <v>-0.2802260515972894</v>
       </c>
       <c r="AG4" t="n">
-        <v>-0.03447034086699631</v>
+        <v>-0.0004806981102348303</v>
       </c>
       <c r="AH4" t="n">
         <v>-0</v>
@@ -2248,7 +2248,7 @@
         <v>0</v>
       </c>
       <c r="AL4" t="n">
-        <v>0.08346482370634739</v>
+        <v>0.03391320067782991</v>
       </c>
       <c r="AM4" t="n">
         <v>-0</v>
@@ -2257,10 +2257,10 @@
         <v>0</v>
       </c>
       <c r="AO4" t="n">
-        <v>0.001425139274130004</v>
+        <v>-0.04382687751844315</v>
       </c>
       <c r="AP4" t="n">
-        <v>-0.08288815890890448</v>
+        <v>0.01800998439388342</v>
       </c>
       <c r="AQ4" t="n">
         <v>-0</v>
@@ -2272,10 +2272,10 @@
         <v>0</v>
       </c>
       <c r="AT4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AU4" t="n">
-        <v>0.4142823062989933</v>
+        <v>0.490930550772916</v>
       </c>
       <c r="AV4" t="n">
         <v>-0</v>
@@ -2284,16 +2284,16 @@
         <v>0</v>
       </c>
       <c r="AX4" t="n">
-        <v>-0.07056162875261536</v>
+        <v>-0.2412630341333792</v>
       </c>
       <c r="AY4" t="n">
-        <v>-0.2195072107427806</v>
+        <v>-0.1060183635823349</v>
       </c>
       <c r="AZ4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BA4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BB4" t="n">
         <v>0</v>
@@ -2302,7 +2302,7 @@
         <v>0</v>
       </c>
       <c r="BD4" t="n">
-        <v>0.1084983479853896</v>
+        <v>-0.03244371999040717</v>
       </c>
       <c r="BE4" t="n">
         <v>0</v>
@@ -2311,52 +2311,52 @@
         <v>0</v>
       </c>
       <c r="BG4" t="n">
-        <v>-0.1511296373082835</v>
+        <v>-0.01743696709524062</v>
       </c>
       <c r="BH4" t="n">
-        <v>-0.1920463743209763</v>
+        <v>-0.08854328880803962</v>
       </c>
       <c r="BI4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BJ4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BK4" t="n">
         <v>0</v>
       </c>
       <c r="BL4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BM4" t="n">
-        <v>0.1430673738132707</v>
+        <v>0.0555858806580355</v>
       </c>
       <c r="BN4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BO4" t="n">
         <v>-0</v>
       </c>
       <c r="BP4" t="n">
-        <v>-0.003506804419984493</v>
+        <v>0.08095184223925117</v>
       </c>
       <c r="BQ4" t="n">
-        <v>0.01774829638850664</v>
+        <v>-0.0353695774531211</v>
       </c>
       <c r="BR4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BS4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BT4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BU4" t="n">
         <v>-0</v>
       </c>
       <c r="BV4" t="n">
-        <v>0.2174578064331273</v>
+        <v>0.2645884054932645</v>
       </c>
       <c r="BW4" t="n">
         <v>0</v>
@@ -2365,10 +2365,10 @@
         <v>0</v>
       </c>
       <c r="BY4" t="n">
-        <v>-0.07027843473932166</v>
+        <v>-0.07607225122038919</v>
       </c>
       <c r="BZ4" t="n">
-        <v>-0.1317131469424722</v>
+        <v>-0.1065766498934343</v>
       </c>
       <c r="CA4" t="n">
         <v>-0</v>
@@ -2383,22 +2383,22 @@
         <v>-0</v>
       </c>
       <c r="CE4" t="n">
-        <v>-0.08493679991571336</v>
+        <v>-0.1128628071677499</v>
       </c>
       <c r="CF4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CG4" t="n">
         <v>-0</v>
       </c>
       <c r="CH4" t="n">
-        <v>-0.005132296706541574</v>
+        <v>0.02940671068759908</v>
       </c>
       <c r="CI4" t="n">
-        <v>0.107260316561954</v>
+        <v>0.05005876308788209</v>
       </c>
       <c r="CJ4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CK4" t="n">
         <v>0</v>
@@ -2410,100 +2410,100 @@
         <v>0</v>
       </c>
       <c r="CN4" t="n">
-        <v>1.411111576022698e-05</v>
+        <v>-0.1176648399683078</v>
       </c>
       <c r="CO4" t="n">
         <v>-0</v>
       </c>
       <c r="CP4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CQ4" t="n">
-        <v>0.01656313510158922</v>
+        <v>0.0987659328249483</v>
       </c>
       <c r="CR4" t="n">
-        <v>-0.02173635870421967</v>
+        <v>0.09696302121904032</v>
       </c>
       <c r="CS4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CT4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CU4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CV4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CW4" t="n">
-        <v>-0.06794519309467903</v>
+        <v>-0.1132667735478171</v>
       </c>
       <c r="CX4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CY4" t="n">
         <v>0</v>
       </c>
       <c r="CZ4" t="n">
-        <v>-0.002517826506811512</v>
+        <v>0.008266387471978583</v>
       </c>
       <c r="DA4" t="n">
-        <v>0.1129463761574095</v>
+        <v>0.07134993351079165</v>
       </c>
       <c r="DB4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DC4" t="n">
         <v>-0</v>
       </c>
       <c r="DD4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DE4" t="n">
         <v>0</v>
       </c>
       <c r="DF4" t="n">
-        <v>-0.04002326517017469</v>
+        <v>-0.04182103570936625</v>
       </c>
       <c r="DG4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DH4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DI4" t="n">
-        <v>0.0444566794875837</v>
+        <v>-0.1773522024170269</v>
       </c>
       <c r="DJ4" t="n">
-        <v>-0.001614683906987056</v>
+        <v>0.05430905562071246</v>
       </c>
       <c r="DK4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DL4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DM4" t="n">
         <v>0</v>
       </c>
       <c r="DN4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DO4" t="n">
-        <v>0.006081052987154392</v>
+        <v>-0.006789881564130029</v>
       </c>
       <c r="DP4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DQ4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DR4" t="n">
-        <v>0.03351720870604942</v>
+        <v>-0.06165173203514228</v>
       </c>
       <c r="DS4" t="n">
-        <v>-0.00651404814989466</v>
+        <v>0.07945600496514979</v>
       </c>
       <c r="DT4" t="n">
         <v>-0</v>
@@ -2512,13 +2512,13 @@
         <v>-0</v>
       </c>
       <c r="DV4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DW4" t="n">
         <v>-0</v>
       </c>
       <c r="DX4" t="n">
-        <v>-0.05777594466092893</v>
+        <v>-0.0203989119697206</v>
       </c>
       <c r="DY4" t="n">
         <v>0</v>
@@ -2527,106 +2527,106 @@
         <v>-0</v>
       </c>
       <c r="EA4" t="n">
-        <v>0.01639577769065341</v>
+        <v>-0.0676568575607339</v>
       </c>
       <c r="EB4" t="n">
-        <v>0.05440360332127209</v>
+        <v>0.03633715307927934</v>
       </c>
       <c r="EC4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ED4" t="n">
         <v>0</v>
       </c>
       <c r="EE4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EF4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EG4" t="n">
-        <v>-0.09693440032671177</v>
+        <v>-0.04598912915854268</v>
       </c>
       <c r="EH4" t="n">
         <v>0</v>
       </c>
       <c r="EI4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EJ4" t="n">
-        <v>0.02439302318152298</v>
+        <v>0.02204225341916105</v>
       </c>
       <c r="EK4" t="n">
-        <v>0.1195640580710318</v>
+        <v>-0.009853383573066175</v>
       </c>
       <c r="EL4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EM4" t="n">
         <v>-0</v>
       </c>
       <c r="EN4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EO4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EP4" t="n">
-        <v>-0.02990216264525762</v>
+        <v>-0.005227696832770167</v>
       </c>
       <c r="EQ4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ER4" t="n">
         <v>-0</v>
       </c>
       <c r="ES4" t="n">
-        <v>-0.01296633880913288</v>
+        <v>-0.01220162516658875</v>
       </c>
       <c r="ET4" t="n">
-        <v>0.07094629067274934</v>
+        <v>0.1364584260180013</v>
       </c>
       <c r="EU4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EV4" t="n">
         <v>0</v>
       </c>
       <c r="EW4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EX4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EY4" t="n">
-        <v>-0.06543195927951648</v>
+        <v>-0.130932432158351</v>
       </c>
       <c r="EZ4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FA4" t="n">
         <v>-0</v>
       </c>
       <c r="FB4" t="n">
-        <v>0.006229404879093165</v>
+        <v>-0.002061555924192711</v>
       </c>
       <c r="FC4" t="n">
-        <v>0.1024537790435004</v>
+        <v>0.03987951912620769</v>
       </c>
       <c r="FD4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FE4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FF4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FG4" t="n">
         <v>0</v>
       </c>
       <c r="FH4" t="n">
-        <v>-0.002535719417640378</v>
+        <v>0.2075057372435904</v>
       </c>
       <c r="FI4" t="n">
         <v>-0</v>
@@ -2635,16 +2635,16 @@
         <v>-0</v>
       </c>
       <c r="FK4" t="n">
-        <v>-0.008508884200727705</v>
+        <v>-0.08888362194263089</v>
       </c>
       <c r="FL4" t="n">
-        <v>0.05172385674770193</v>
+        <v>0.1169911234280748</v>
       </c>
       <c r="FM4" t="n">
         <v>0</v>
       </c>
       <c r="FN4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FO4" t="n">
         <v>0</v>
@@ -2653,46 +2653,46 @@
         <v>0</v>
       </c>
       <c r="FQ4" t="n">
-        <v>0.004963051982165477</v>
+        <v>0.01095474566180105</v>
       </c>
       <c r="FR4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FS4" t="n">
         <v>-0</v>
       </c>
       <c r="FT4" t="n">
-        <v>-0.008810654514323803</v>
+        <v>-0.02433236845990461</v>
       </c>
       <c r="FU4" t="n">
-        <v>0.03438754936987051</v>
+        <v>-0.04959525460895942</v>
       </c>
       <c r="FV4" t="n">
         <v>-0</v>
       </c>
       <c r="FW4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FX4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FY4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FZ4" t="n">
-        <v>0.04462418624405818</v>
+        <v>-0.0392241248176862</v>
       </c>
       <c r="GA4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GB4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GC4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GD4" t="n">
-        <v>-0.05108333755087999</v>
+        <v>0.06229019800014492</v>
       </c>
       <c r="GE4" t="n">
         <v>-0</v>
@@ -2701,7 +2701,7 @@
         <v>-0</v>
       </c>
       <c r="GG4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5">
@@ -3847,7 +3847,7 @@
         <v>0</v>
       </c>
       <c r="B7" t="n">
-        <v>0.1555227955103367</v>
+        <v>0.3740873085411197</v>
       </c>
       <c r="C7" t="n">
         <v>0</v>
@@ -3856,25 +3856,25 @@
         <v>0</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.08280241633837762</v>
+        <v>-0.01212069175337799</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.07228254118439849</v>
+        <v>-0.1420221622722794</v>
       </c>
       <c r="G7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="H7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="I7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J7" t="n">
         <v>0</v>
       </c>
       <c r="K7" t="n">
-        <v>0.1280013609926359</v>
+        <v>0.4550155857997566</v>
       </c>
       <c r="L7" t="n">
         <v>0</v>
@@ -3883,25 +3883,25 @@
         <v>0</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.05768573777505789</v>
+        <v>-0.1030346101625517</v>
       </c>
       <c r="O7" t="n">
-        <v>-0.07598714090533507</v>
+        <v>-0.1872297503630286</v>
       </c>
       <c r="P7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Q7" t="n">
         <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="S7" t="n">
         <v>0</v>
       </c>
       <c r="T7" t="n">
-        <v>0.01378244307605709</v>
+        <v>0.08850790259557874</v>
       </c>
       <c r="U7" t="n">
         <v>0</v>
@@ -3910,40 +3910,40 @@
         <v>0</v>
       </c>
       <c r="W7" t="n">
-        <v>-0.004451178988662641</v>
+        <v>-0.08737791763617689</v>
       </c>
       <c r="X7" t="n">
-        <v>0.009296517155136153</v>
+        <v>-0.01195679459117023</v>
       </c>
       <c r="Y7" t="n">
         <v>-0</v>
       </c>
       <c r="Z7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA7" t="n">
         <v>0</v>
       </c>
       <c r="AB7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AC7" t="n">
-        <v>-0.004937052603166965</v>
+        <v>-0.03445648712941773</v>
       </c>
       <c r="AD7" t="n">
         <v>-0</v>
       </c>
       <c r="AE7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AF7" t="n">
-        <v>0.01397086337945391</v>
+        <v>-0.2456376296061947</v>
       </c>
       <c r="AG7" t="n">
-        <v>0.01246458326384953</v>
+        <v>0.01208147322881906</v>
       </c>
       <c r="AH7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AI7" t="n">
         <v>-0</v>
@@ -3955,22 +3955,22 @@
         <v>0</v>
       </c>
       <c r="AL7" t="n">
-        <v>0.01048426267962558</v>
+        <v>0.03864887039576933</v>
       </c>
       <c r="AM7" t="n">
         <v>-0</v>
       </c>
       <c r="AN7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AO7" t="n">
-        <v>-0.008843058167262783</v>
+        <v>-0.03478953138166604</v>
       </c>
       <c r="AP7" t="n">
-        <v>-0.01472490147678882</v>
+        <v>0.004348853773135694</v>
       </c>
       <c r="AQ7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AR7" t="n">
         <v>-0</v>
@@ -3979,28 +3979,28 @@
         <v>0</v>
       </c>
       <c r="AT7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AU7" t="n">
-        <v>0.1072825700670186</v>
+        <v>0.4082565567656767</v>
       </c>
       <c r="AV7" t="n">
         <v>-0</v>
       </c>
       <c r="AW7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AX7" t="n">
-        <v>-0.02880010261672456</v>
+        <v>-0.2569226983256364</v>
       </c>
       <c r="AY7" t="n">
-        <v>-0.02119212093019258</v>
+        <v>-0.1019174011449789</v>
       </c>
       <c r="AZ7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BA7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BB7" t="n">
         <v>0</v>
@@ -4009,7 +4009,7 @@
         <v>0</v>
       </c>
       <c r="BD7" t="n">
-        <v>0.03149636970574076</v>
+        <v>-0.007966828915457077</v>
       </c>
       <c r="BE7" t="n">
         <v>0</v>
@@ -4018,52 +4018,52 @@
         <v>0</v>
       </c>
       <c r="BG7" t="n">
-        <v>-0.05775229627875221</v>
+        <v>0.003299825105484479</v>
       </c>
       <c r="BH7" t="n">
-        <v>-0.05909104473704765</v>
+        <v>-0.06672767056896817</v>
       </c>
       <c r="BI7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BJ7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BK7" t="n">
         <v>0</v>
       </c>
       <c r="BL7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BM7" t="n">
-        <v>0.03556435611813727</v>
+        <v>0.03790515352353375</v>
       </c>
       <c r="BN7" t="n">
         <v>-0</v>
       </c>
       <c r="BO7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BP7" t="n">
-        <v>0.0160377211932141</v>
+        <v>0.05412149956945281</v>
       </c>
       <c r="BQ7" t="n">
-        <v>0.01704690532514525</v>
+        <v>-0.02904912448350688</v>
       </c>
       <c r="BR7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BS7" t="n">
         <v>-0</v>
       </c>
       <c r="BT7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BU7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BV7" t="n">
-        <v>0.05103091105067987</v>
+        <v>0.2284431608214726</v>
       </c>
       <c r="BW7" t="n">
         <v>0</v>
@@ -4072,10 +4072,10 @@
         <v>0</v>
       </c>
       <c r="BY7" t="n">
-        <v>-0.01218046926464564</v>
+        <v>-0.06484531704446789</v>
       </c>
       <c r="BZ7" t="n">
-        <v>-0.01384008897907786</v>
+        <v>-0.108101791999787</v>
       </c>
       <c r="CA7" t="n">
         <v>-0</v>
@@ -4084,31 +4084,31 @@
         <v>-0</v>
       </c>
       <c r="CC7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CD7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CE7" t="n">
-        <v>-0.02622308846222178</v>
+        <v>-0.106248834828522</v>
       </c>
       <c r="CF7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CG7" t="n">
         <v>-0</v>
       </c>
       <c r="CH7" t="n">
-        <v>0.007127736093176795</v>
+        <v>0.02637823890535754</v>
       </c>
       <c r="CI7" t="n">
-        <v>0.01772200217820961</v>
+        <v>0.05235108424751526</v>
       </c>
       <c r="CJ7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CK7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CL7" t="n">
         <v>0</v>
@@ -4117,52 +4117,52 @@
         <v>0</v>
       </c>
       <c r="CN7" t="n">
-        <v>0.0008607606247808709</v>
+        <v>-0.1167963372686887</v>
       </c>
       <c r="CO7" t="n">
         <v>-0</v>
       </c>
       <c r="CP7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CQ7" t="n">
-        <v>-0.007075855757484145</v>
+        <v>0.1418910920064637</v>
       </c>
       <c r="CR7" t="n">
-        <v>-0.01179765717120735</v>
+        <v>0.06948314519810558</v>
       </c>
       <c r="CS7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CT7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CU7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CV7" t="n">
         <v>-0</v>
       </c>
       <c r="CW7" t="n">
-        <v>-0.01997228527183853</v>
+        <v>-0.1042914444843911</v>
       </c>
       <c r="CX7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CY7" t="n">
         <v>0</v>
       </c>
       <c r="CZ7" t="n">
-        <v>0.006098553888960175</v>
+        <v>0.01336787605902164</v>
       </c>
       <c r="DA7" t="n">
-        <v>0.01817422480022265</v>
+        <v>0.07393732256271993</v>
       </c>
       <c r="DB7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DC7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DD7" t="n">
         <v>0</v>
@@ -4171,22 +4171,22 @@
         <v>0</v>
       </c>
       <c r="DF7" t="n">
-        <v>-0.03236358042313904</v>
+        <v>-0.07613463879940778</v>
       </c>
       <c r="DG7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DH7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DI7" t="n">
-        <v>0.05139714038333401</v>
+        <v>-0.2088158290936235</v>
       </c>
       <c r="DJ7" t="n">
-        <v>0.01369322867674388</v>
+        <v>0.0664830782668345</v>
       </c>
       <c r="DK7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DL7" t="n">
         <v>-0</v>
@@ -4195,28 +4195,28 @@
         <v>0</v>
       </c>
       <c r="DN7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DO7" t="n">
-        <v>-0.005787316285419271</v>
+        <v>-0.01453139399809695</v>
       </c>
       <c r="DP7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DQ7" t="n">
         <v>0</v>
       </c>
       <c r="DR7" t="n">
-        <v>0.01937102480609069</v>
+        <v>-0.04380413370108927</v>
       </c>
       <c r="DS7" t="n">
-        <v>-0.009748317299426336</v>
+        <v>0.04598420032442908</v>
       </c>
       <c r="DT7" t="n">
         <v>-0</v>
       </c>
       <c r="DU7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DV7" t="n">
         <v>-0</v>
@@ -4225,49 +4225,49 @@
         <v>-0</v>
       </c>
       <c r="DX7" t="n">
-        <v>-0.02951577427682513</v>
+        <v>-0.008128724834928856</v>
       </c>
       <c r="DY7" t="n">
         <v>0</v>
       </c>
       <c r="DZ7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EA7" t="n">
-        <v>0.01498315768491325</v>
+        <v>-0.05739258479727879</v>
       </c>
       <c r="EB7" t="n">
-        <v>0.01825960522851271</v>
+        <v>0.02186635189298738</v>
       </c>
       <c r="EC7" t="n">
         <v>-0</v>
       </c>
       <c r="ED7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EE7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EF7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EG7" t="n">
-        <v>-0.0315053328593496</v>
+        <v>-0.04910027289638845</v>
       </c>
       <c r="EH7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EI7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EJ7" t="n">
-        <v>0.00944317674849344</v>
+        <v>0.009966225733988959</v>
       </c>
       <c r="EK7" t="n">
-        <v>0.01334605781814872</v>
+        <v>-0.0008290111176221996</v>
       </c>
       <c r="EL7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EM7" t="n">
         <v>-0</v>
@@ -4276,82 +4276,82 @@
         <v>-0</v>
       </c>
       <c r="EO7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EP7" t="n">
-        <v>-0.01243019102766987</v>
+        <v>-0.03263751016830274</v>
       </c>
       <c r="EQ7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ER7" t="n">
         <v>-0</v>
       </c>
       <c r="ES7" t="n">
-        <v>0.002243096035829807</v>
+        <v>-0.01666909488296208</v>
       </c>
       <c r="ET7" t="n">
-        <v>-0.01165242559899074</v>
+        <v>0.1081606505080878</v>
       </c>
       <c r="EU7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EV7" t="n">
         <v>0</v>
       </c>
       <c r="EW7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EX7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EY7" t="n">
-        <v>-0.0208915055260241</v>
+        <v>-0.1236182570442468</v>
       </c>
       <c r="EZ7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FA7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FB7" t="n">
-        <v>0.009264301360075101</v>
+        <v>0.001119420975175839</v>
       </c>
       <c r="FC7" t="n">
-        <v>0.02170654796978215</v>
+        <v>0.04480882699908054</v>
       </c>
       <c r="FD7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FE7" t="n">
         <v>-0</v>
       </c>
       <c r="FF7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FG7" t="n">
         <v>0</v>
       </c>
       <c r="FH7" t="n">
-        <v>-0.01511337365004362</v>
+        <v>0.1682489665630392</v>
       </c>
       <c r="FI7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FJ7" t="n">
         <v>-0</v>
       </c>
       <c r="FK7" t="n">
-        <v>0.0113268961668335</v>
+        <v>-0.08182097191585727</v>
       </c>
       <c r="FL7" t="n">
-        <v>0.01985781488408164</v>
+        <v>0.1168730928665216</v>
       </c>
       <c r="FM7" t="n">
         <v>0</v>
       </c>
       <c r="FN7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FO7" t="n">
         <v>0</v>
@@ -4360,63 +4360,63 @@
         <v>0</v>
       </c>
       <c r="FQ7" t="n">
-        <v>7.644719732458803e-05</v>
+        <v>0.001766033095943371</v>
       </c>
       <c r="FR7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FS7" t="n">
         <v>-0</v>
       </c>
       <c r="FT7" t="n">
-        <v>-0.001509859052916248</v>
+        <v>-0.008890543018079875</v>
       </c>
       <c r="FU7" t="n">
-        <v>0.01880918805336776</v>
+        <v>-0.02826654740530361</v>
       </c>
       <c r="FV7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FW7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FX7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FY7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FZ7" t="n">
-        <v>0.001820653164314721</v>
+        <v>-0.03526500023485375</v>
       </c>
       <c r="GA7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GB7" t="n">
         <v>-0</v>
       </c>
       <c r="GC7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GD7" t="n">
-        <v>-0.005457780234660795</v>
+        <v>0.06675703004937075</v>
       </c>
       <c r="GE7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GF7" t="n">
         <v>-0</v>
       </c>
       <c r="GG7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>0.1266462604957166</v>
+        <v>0.2568294364946774</v>
       </c>
       <c r="B8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="C8" t="n">
         <v>0</v>
@@ -4425,10 +4425,10 @@
         <v>0</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.0359596502453245</v>
+        <v>0.08360029537802897</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.1458807809284861</v>
+        <v>-0.1124021230301778</v>
       </c>
       <c r="G8" t="n">
         <v>0</v>
@@ -4437,10 +4437,10 @@
         <v>-0</v>
       </c>
       <c r="I8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J8" t="n">
-        <v>0.1005695273084039</v>
+        <v>0.2217196001047798</v>
       </c>
       <c r="K8" t="n">
         <v>-0</v>
@@ -4449,43 +4449,43 @@
         <v>0</v>
       </c>
       <c r="M8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.002737779122467324</v>
+        <v>-0.007165351043765546</v>
       </c>
       <c r="O8" t="n">
-        <v>-0.0997243053547566</v>
+        <v>-0.1079803910484537</v>
       </c>
       <c r="P8" t="n">
         <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="R8" t="n">
         <v>-0</v>
       </c>
       <c r="S8" t="n">
-        <v>0.01760666690443216</v>
+        <v>-0.06928175277144705</v>
       </c>
       <c r="T8" t="n">
         <v>0</v>
       </c>
       <c r="U8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="V8" t="n">
         <v>0</v>
       </c>
       <c r="W8" t="n">
-        <v>-0.03898100455986269</v>
+        <v>-0.04621480493013201</v>
       </c>
       <c r="X8" t="n">
-        <v>-0.02367567826519899</v>
+        <v>-0.08056909819103956</v>
       </c>
       <c r="Y8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z8" t="n">
         <v>0</v>
@@ -4494,7 +4494,7 @@
         <v>0</v>
       </c>
       <c r="AB8" t="n">
-        <v>0.01516222809156062</v>
+        <v>0.0545615304003013</v>
       </c>
       <c r="AC8" t="n">
         <v>0</v>
@@ -4503,43 +4503,43 @@
         <v>0</v>
       </c>
       <c r="AE8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AF8" t="n">
-        <v>-0.02746700724001907</v>
+        <v>-0.03953367418522752</v>
       </c>
       <c r="AG8" t="n">
-        <v>-0.02875747820365326</v>
+        <v>0.05219803461472458</v>
       </c>
       <c r="AH8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AI8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AJ8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AK8" t="n">
-        <v>0.02170311454758471</v>
+        <v>0.01635961694893267</v>
       </c>
       <c r="AL8" t="n">
         <v>0</v>
       </c>
       <c r="AM8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AN8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AO8" t="n">
-        <v>-0.007094937415410008</v>
+        <v>0.0310684134670413</v>
       </c>
       <c r="AP8" t="n">
-        <v>-0.01299687962429524</v>
+        <v>0.01725490832228489</v>
       </c>
       <c r="AQ8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AR8" t="n">
         <v>0</v>
@@ -4548,25 +4548,25 @@
         <v>0</v>
       </c>
       <c r="AT8" t="n">
-        <v>0.08472652476482592</v>
+        <v>-0.0180578642833223</v>
       </c>
       <c r="AU8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AV8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AW8" t="n">
         <v>0</v>
       </c>
       <c r="AX8" t="n">
-        <v>-0.1007914678233191</v>
+        <v>0.08887558904301493</v>
       </c>
       <c r="AY8" t="n">
-        <v>-0.08600565149370705</v>
+        <v>-0.007113253437926324</v>
       </c>
       <c r="AZ8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BA8" t="n">
         <v>0</v>
@@ -4575,22 +4575,22 @@
         <v>0</v>
       </c>
       <c r="BC8" t="n">
-        <v>0.01499549256361632</v>
+        <v>0.1617831854512066</v>
       </c>
       <c r="BD8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BE8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BF8" t="n">
         <v>0</v>
       </c>
       <c r="BG8" t="n">
-        <v>0.01190784752073141</v>
+        <v>-0.02019540684000256</v>
       </c>
       <c r="BH8" t="n">
-        <v>-0.04702454220862393</v>
+        <v>0.002295561210419389</v>
       </c>
       <c r="BI8" t="n">
         <v>0</v>
@@ -4602,10 +4602,10 @@
         <v>-0</v>
       </c>
       <c r="BL8" t="n">
-        <v>0.007487808577764449</v>
+        <v>-0.06679451029213296</v>
       </c>
       <c r="BM8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BN8" t="n">
         <v>-0</v>
@@ -4614,37 +4614,37 @@
         <v>0</v>
       </c>
       <c r="BP8" t="n">
-        <v>0.003610416424803363</v>
+        <v>-0.1113391538630767</v>
       </c>
       <c r="BQ8" t="n">
-        <v>0.008104688305153049</v>
+        <v>0.03653506681344443</v>
       </c>
       <c r="BR8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BS8" t="n">
         <v>0</v>
       </c>
       <c r="BT8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BU8" t="n">
-        <v>0.03643594286452657</v>
+        <v>-0.02642080760106553</v>
       </c>
       <c r="BV8" t="n">
         <v>0</v>
       </c>
       <c r="BW8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BX8" t="n">
         <v>0</v>
       </c>
       <c r="BY8" t="n">
-        <v>-0.03598242985426318</v>
+        <v>-0.0702652693062062</v>
       </c>
       <c r="BZ8" t="n">
-        <v>-0.06421245250715174</v>
+        <v>-0.1104025499013803</v>
       </c>
       <c r="CA8" t="n">
         <v>-0</v>
@@ -4653,10 +4653,10 @@
         <v>0</v>
       </c>
       <c r="CC8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CD8" t="n">
-        <v>-0.02249073403637856</v>
+        <v>-0.06422544393623388</v>
       </c>
       <c r="CE8" t="n">
         <v>0</v>
@@ -4668,13 +4668,13 @@
         <v>0</v>
       </c>
       <c r="CH8" t="n">
-        <v>0.01066464430794283</v>
+        <v>0.007021126430780321</v>
       </c>
       <c r="CI8" t="n">
-        <v>0.04343561869056956</v>
+        <v>0.03115380220022167</v>
       </c>
       <c r="CJ8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CK8" t="n">
         <v>0</v>
@@ -4683,25 +4683,25 @@
         <v>-0</v>
       </c>
       <c r="CM8" t="n">
-        <v>0.004126862283695319</v>
+        <v>0.01181028276288585</v>
       </c>
       <c r="CN8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CO8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CP8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CQ8" t="n">
-        <v>0.06820944344543946</v>
+        <v>0.08373939567032432</v>
       </c>
       <c r="CR8" t="n">
-        <v>0.001346799260798693</v>
+        <v>-0.04380478783386278</v>
       </c>
       <c r="CS8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CT8" t="n">
         <v>-0</v>
@@ -4710,7 +4710,7 @@
         <v>-0</v>
       </c>
       <c r="CV8" t="n">
-        <v>-0.02108001772460196</v>
+        <v>-0.06726026660128644</v>
       </c>
       <c r="CW8" t="n">
         <v>-0</v>
@@ -4722,40 +4722,40 @@
         <v>-0</v>
       </c>
       <c r="CZ8" t="n">
-        <v>0.01460815439289092</v>
+        <v>0.004563328884568592</v>
       </c>
       <c r="DA8" t="n">
-        <v>0.03937246904179714</v>
+        <v>0.03598994833441783</v>
       </c>
       <c r="DB8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DC8" t="n">
         <v>-0</v>
       </c>
       <c r="DD8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DE8" t="n">
-        <v>-0.0001534932277220459</v>
+        <v>-0.005146031250466448</v>
       </c>
       <c r="DF8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DG8" t="n">
         <v>-0</v>
       </c>
       <c r="DH8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DI8" t="n">
-        <v>0.03079357996395915</v>
+        <v>-0.06032322361351384</v>
       </c>
       <c r="DJ8" t="n">
-        <v>0.001550474019576347</v>
+        <v>0.01431398112090277</v>
       </c>
       <c r="DK8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DL8" t="n">
         <v>0</v>
@@ -4764,7 +4764,7 @@
         <v>0</v>
       </c>
       <c r="DN8" t="n">
-        <v>-0.0005372762060466832</v>
+        <v>-0.03987372890085466</v>
       </c>
       <c r="DO8" t="n">
         <v>0</v>
@@ -4773,13 +4773,13 @@
         <v>0</v>
       </c>
       <c r="DQ8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DR8" t="n">
-        <v>0.03730876190525402</v>
+        <v>-0.05332094162376333</v>
       </c>
       <c r="DS8" t="n">
-        <v>0.01723860783134225</v>
+        <v>0.08169112504517606</v>
       </c>
       <c r="DT8" t="n">
         <v>-0</v>
@@ -4788,37 +4788,37 @@
         <v>0</v>
       </c>
       <c r="DV8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DW8" t="n">
-        <v>-0.008746059748456648</v>
+        <v>0.02465871043844876</v>
       </c>
       <c r="DX8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DY8" t="n">
         <v>-0</v>
       </c>
       <c r="DZ8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EA8" t="n">
-        <v>0.01650795672862657</v>
+        <v>0.1237911810008313</v>
       </c>
       <c r="EB8" t="n">
-        <v>0.03860945368572078</v>
+        <v>0.06352424167544639</v>
       </c>
       <c r="EC8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="ED8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EE8" t="n">
         <v>0</v>
       </c>
       <c r="EF8" t="n">
-        <v>-0.02203262574153988</v>
+        <v>0.003466002153019663</v>
       </c>
       <c r="EG8" t="n">
         <v>0</v>
@@ -4830,22 +4830,22 @@
         <v>0</v>
       </c>
       <c r="EJ8" t="n">
-        <v>-0.003408451035381646</v>
+        <v>-0.02625681375732344</v>
       </c>
       <c r="EK8" t="n">
-        <v>0.04728923408716374</v>
+        <v>0.0510532135942809</v>
       </c>
       <c r="EL8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EM8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EN8" t="n">
         <v>0</v>
       </c>
       <c r="EO8" t="n">
-        <v>-0.01277627041603102</v>
+        <v>-0.03844273207820576</v>
       </c>
       <c r="EP8" t="n">
         <v>0</v>
@@ -4854,13 +4854,13 @@
         <v>-0</v>
       </c>
       <c r="ER8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ES8" t="n">
-        <v>0.02803751493072065</v>
+        <v>0.006067814825159359</v>
       </c>
       <c r="ET8" t="n">
-        <v>0.002817743768328517</v>
+        <v>0.04406886628997701</v>
       </c>
       <c r="EU8" t="n">
         <v>0</v>
@@ -4872,7 +4872,7 @@
         <v>-0</v>
       </c>
       <c r="EX8" t="n">
-        <v>-0.01808398236400945</v>
+        <v>-0.05967497713790787</v>
       </c>
       <c r="EY8" t="n">
         <v>0</v>
@@ -4884,22 +4884,22 @@
         <v>0</v>
       </c>
       <c r="FB8" t="n">
-        <v>0.02408577528846209</v>
+        <v>-0.006747037493913817</v>
       </c>
       <c r="FC8" t="n">
-        <v>0.04115578127544132</v>
+        <v>0.04533085295682484</v>
       </c>
       <c r="FD8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FE8" t="n">
         <v>0</v>
       </c>
       <c r="FF8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FG8" t="n">
-        <v>0.007376195651755181</v>
+        <v>0.127769368547643</v>
       </c>
       <c r="FH8" t="n">
         <v>-0</v>
@@ -4908,13 +4908,13 @@
         <v>0</v>
       </c>
       <c r="FJ8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FK8" t="n">
-        <v>0.01202097803954294</v>
+        <v>-5.861337664423544e-05</v>
       </c>
       <c r="FL8" t="n">
-        <v>-0.002121784118489793</v>
+        <v>0.1059281336776556</v>
       </c>
       <c r="FM8" t="n">
         <v>0</v>
@@ -4926,10 +4926,10 @@
         <v>-0</v>
       </c>
       <c r="FP8" t="n">
-        <v>0.0006546982649096399</v>
+        <v>0.003074093359563177</v>
       </c>
       <c r="FQ8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FR8" t="n">
         <v>-0</v>
@@ -4938,13 +4938,13 @@
         <v>0</v>
       </c>
       <c r="FT8" t="n">
-        <v>-0.0006216824476783274</v>
+        <v>0.001590208613466223</v>
       </c>
       <c r="FU8" t="n">
-        <v>0.01139849522618542</v>
+        <v>0.04096364891334509</v>
       </c>
       <c r="FV8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FW8" t="n">
         <v>-0</v>
@@ -4953,28 +4953,28 @@
         <v>0</v>
       </c>
       <c r="FY8" t="n">
-        <v>0.00460258118434362</v>
+        <v>0.0725763631748053</v>
       </c>
       <c r="FZ8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GA8" t="n">
         <v>0</v>
       </c>
       <c r="GB8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GC8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GD8" t="n">
-        <v>0.01054367872908787</v>
+        <v>0.07896609230274053</v>
       </c>
       <c r="GE8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GF8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GG8" t="n">
         <v>0</v>
